--- a/src/test/fixtures/forms-responses-http/extra-fields-export-en.xlsx
+++ b/src/test/fixtures/forms-responses-http/extra-fields-export-en.xlsx
@@ -42,7 +42,7 @@
     <x:t>Suppliers · Retired field</x:t>
   </x:si>
   <x:si>
-    <x:t>TDA86EFC1-000001</x:t>
+    <x:t>T6E4D1379-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Unavailable</x:t>
@@ -60,7 +60,7 @@
     <x:t>historical; historical</x:t>
   </x:si>
   <x:si>
-    <x:t>TDA86EFC1-000002</x:t>
+    <x:t>T6E4D1379-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Primero histórico</x:t>
@@ -69,7 +69,7 @@
     <x:t>—</x:t>
   </x:si>
   <x:si>
-    <x:t>TDA86EFC1-000003</x:t>
+    <x:t>T6E4D1379-000003</x:t>
   </x:si>
 </x:sst>
 </file>
